--- a/Result/profitability/1538.xlsx
+++ b/Result/profitability/1538.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.385</v>
+        <v>-0.4187499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>17.7</v>
+        <v>19.4075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1637500000000001</v>
+        <v>0.08500000000000008</v>
       </c>
       <c r="N3" t="n">
-        <v>17.53875</v>
+        <v>17.36625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2100000000000001</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>15.41875</v>
+        <v>14.47625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1637500000000001</v>
+        <v>-0.0487499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>16.25125</v>
+        <v>16.2175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05000000000000006</v>
+        <v>0.07000000000000009</v>
       </c>
       <c r="N6" t="n">
-        <v>16.13</v>
+        <v>14.87375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1012500000000001</v>
+        <v>0.1725000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>14.78875</v>
+        <v>12.6125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.235</v>
+        <v>0.2912500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>12.98875</v>
+        <v>12.88125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9810,6 +9810,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>24</v>
+      </c>
+      <c r="D75" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-58.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4724999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.81125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4054054054054055</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8599999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05481198215423833</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.634615384615385</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2699999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01788079470198678</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
